--- a/preproc/Provo_stimuli.xlsx
+++ b/preproc/Provo_stimuli.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin\Documents\R\WebEye\preproc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF823D8-E85C-402F-B040-5906D7D60BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3450253-30B9-427F-8693-0F35371CF3B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{54C585F9-79A6-411C-9B6D-9060C6BA081E}"/>
   </bookViews>
@@ -47,9 +47,6 @@
     <t>Text</t>
   </si>
   <si>
-    <t>Two days later, the@British astronomer@Richard Carrington@ was observing the</t>
-  </si>
-  <si>
     <t>telescope when he saw@what he described as "two patches of@intensely bright and </t>
   </si>
   <si>
@@ -120,6 +117,9 @@
   </si>
   <si>
     <t>Michael Larson wanted@to empty his whole@bank account.</t>
+  </si>
+  <si>
+    <t>Two days later, the@British astronomer@Richard Carrington@was observing the</t>
   </si>
 </sst>
 </file>
@@ -519,7 +519,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -530,7 +530,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -541,7 +541,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -552,7 +552,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -563,7 +563,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -574,7 +574,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -585,7 +585,7 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -596,7 +596,7 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -607,7 +607,7 @@
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -618,7 +618,7 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
@@ -629,7 +629,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -640,7 +640,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
@@ -651,7 +651,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
@@ -662,7 +662,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
@@ -673,7 +673,7 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
@@ -684,7 +684,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
@@ -695,7 +695,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
@@ -706,7 +706,7 @@
         <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
@@ -717,7 +717,7 @@
         <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
@@ -728,7 +728,7 @@
         <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
@@ -739,7 +739,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
@@ -750,7 +750,7 @@
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -761,7 +761,7 @@
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -772,7 +772,7 @@
         <v>4</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
@@ -783,7 +783,7 @@
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
